--- a/data/추가검사항목.xlsx
+++ b/data/추가검사항목.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -654,11 +654,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>관상동맥칼슘 CT</t>
+          <t>패치형 심전도 모니터링 (S-Patch)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D10" s="2" t="n"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>위내시경 수면요법</t>
+          <t>내시경 시 수면요법</t>
         </is>
       </c>
       <c r="C22" s="6" t="n">
@@ -997,6 +997,22 @@
         <v>1000000</v>
       </c>
       <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>내분비계</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>CGM연속혈당모니터링</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
